--- a/光伏配储项目/电价数据/2026/凌霄站.xlsx
+++ b/光伏配储项目/电价数据/2026/凌霄站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.50979</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38224</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.70884</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.56511</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.51685</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.45643</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.45109</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.43781</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.45462</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.43923</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.42321</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.41932</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.40889</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.3984</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.40015</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.38522</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.40212</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.42335</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.41283</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35485</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.39177</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.38508</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.41723</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39203</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.42072</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.4142</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.42419</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.41302</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.44418</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.35718</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.2999</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.33398</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.26144</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.29487</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.29909</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.21926</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.26155</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.07912000000000001</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.06534000000000001</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.05481</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.0351</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.05694</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.03851</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.04659000000000001</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.01327</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>-0.01931</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.08601</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>-0.01913</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.00032</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.00128</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.1448</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.21283</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.23478</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.1858</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.12096</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>-0.01191</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>-0.00984</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.1192</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.11839</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.17839</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.22504</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.17933</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.15193</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.12485</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.19673</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.27917</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.0123</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.24377</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>0.04243</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.3599</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>0.46607</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.37144</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.43028</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.35674</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.52883</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.35685</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>0.4871</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>0.74314</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>0.61129</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>0.5192899999999999</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>0.52547</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>0.07804000000000001</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.3841</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.58489</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.54215</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>0.28232</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.50385</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.50539</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.60109</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.56114</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.43527</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.48008</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.40086</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41328</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42252</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.33016</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.62874</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.43048</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.74522</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.02346</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.79876</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.5366799999999999</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.52396</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.50663</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.50746</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.50217</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.39492</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.47428</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.37424</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.3812</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.39248</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33788</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.3716</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35704</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.36019</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.37653</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.37645</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.36045</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.38139</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.4229</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.51652</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.6289199999999999</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.71976</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.4374</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.35568</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.39025</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34642</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.32644</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.34086</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.45277</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.09409999999999999</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.30813</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.3071</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>-0.03695</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.26714</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.30178</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.27204</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.27946</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.31194</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.25762</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.37557</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.6136699999999999</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.25199</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.28143</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.28605</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.30836</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.30908</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.26114</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.58963</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.40032</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.34482</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>-0.00483</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.27285</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.2982</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.31484</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.30069</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.3058</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.33388</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.24117</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.17847</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.24024</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.24706</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.23262</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>0.25097</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>0.39767</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>0.40421</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>0.29189</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.25835</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>0.329</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>0.36164</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>0.46757</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>0.28667</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>0.68771</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.79311</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.78706</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.26994</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.34803</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.80367</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>0.35887</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.36675</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>0.78308</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.29394</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.43549</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.5893200000000001</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.43863</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.43285</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.40713</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33197</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.3762200000000001</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35359</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33354</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.3216</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.5149900000000001</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.36887</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.46514</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.36041</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.38057</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.40123</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.38372</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.39051</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38194</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.3616</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.43231</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.44837</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33559</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37118</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39385</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.3651</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.36985</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35319</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.3585</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.34843</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.36298</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35609</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.38005</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39646</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47399</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.44807</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.44243</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34819</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.39597</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35262</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36789</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34649</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.27934</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.28282</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.2768</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.31073</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.14317</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.27783</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.25324</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.30778</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.31027</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.30129</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.28333</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.33777</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.41461</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.359</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.41268</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.25273</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.41111</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.28164</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.28066</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.07745999999999999</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.22131</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.15743</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.21483</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.20185</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.25072</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.29217</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.33637</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.29908</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.27987</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.334</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.32785</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.28221</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.32094</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.3042</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.24191</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.21802</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>0.03288</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.28986</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.31523</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.30656</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.31874</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.37151</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.48461</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.03276</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.5076700000000001</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.31394</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.32579</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.31311</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.30365</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.32364</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.30262</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.3779</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.39857</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.38472</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.30819</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.31381</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.33516</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.32304</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.35679</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.35523</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.34309</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.3499</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34338</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.32017</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.31126</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.35697</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.31804</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.33609</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.32656</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.34598</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.33484</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.3274</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.32794</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.30142</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.30107</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.47006</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.31223</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.31864</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.30118</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.31662</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.31733</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.29616</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.29822</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.29514</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.29401</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.29555</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.33915</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33923</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.36002</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.34148</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.39017</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.31825</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.32727</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.31061</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.32055</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.3395899999999999</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.31274</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.2824</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.2631</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.22168</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.1376</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.1336</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.09794</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.26745</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.22647</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.13455</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.28745</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.45983</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.28891</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.37327</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.22046</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>-0.03514</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>-0.03976</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.06576</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.2655</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.21468</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.0604</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.01305</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.29417</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.00074</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.04846</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.08904000000000001</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.12125</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.35581</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.32002</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.25378</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.19538</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.2237</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.18271</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.23253</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.16225</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.23688</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.25267</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.29019</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.33437</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.31213</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.33679</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.27786</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.29247</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.30918</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.41976</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.48506</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.41023</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.39628</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.32354</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.32107</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.32869</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.33841</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.30993</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.31284</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.30763</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.27864</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.3075</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32128</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.29421</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.28983</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.29997</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.28783</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.29095</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.29724</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.36508</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.40198</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.36417</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.34687</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.30122</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.31097</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.30965</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.30682</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.30273</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.28431</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.30764</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.30354</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.2835299999999999</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.28706</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.29018</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.29018</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.29023</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.29215</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.29515</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31235</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.30407</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31648</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32436</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32427</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33284</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32606</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.27934</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.26052</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.04012</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.04534000000000001</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.03992</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.03978</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.04298</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.04623</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.04459</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.04661999999999999</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>-0.04177</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>-0.04955</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>-0.04649</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>-0.04603</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>-0.0444</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>-0.04453</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>-0.04556</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>-0.04448</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>-0.04342</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>-0.04584000000000001</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>-0.04912</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>-0.04495</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>-0.04562</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>-0.04709000000000001</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>-0.047</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>-0.04943</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>-0.04494</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>-0.04694</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.22033</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.04734</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.05138</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.05353</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>-0.0026</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.14646</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.03686</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.09842000000000001</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.28968</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.29185</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.29306</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31984</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32941</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31431</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33493</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.33024</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33134</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.32387</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.37495</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.38815</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.38303</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.37787</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.34128</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.40073</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39725</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.41201</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46765</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.35389</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39654</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.40017</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.41762</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35505</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35811</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34527</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35518</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.35139</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.36802</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.6635599999999999</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.40013</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.4466</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.4238</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.42389</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.35995</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.35937</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.35906</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.33465</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.31029</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.32564</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.3579</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.35659</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.34865</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.34744</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.33507</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.31552</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.33031</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.33561</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.3228</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.30015</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.32287</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33542</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.33912</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.35031</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.35212</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.34295</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.31619</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10242</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04246</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04629</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04581</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04534000000000001</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04535</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04534000000000001</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04457</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.0426</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>-0.03194</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>-0.04139</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.10653</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.00041</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>-0.03766</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>-0.04707</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>-0.04213</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04223</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04212</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.0444</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.04431</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.0443</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04208</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04152</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04402</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04133</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.03985</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.04494</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04403</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04432</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04187</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04291</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>-0.04051</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>-0.04297</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.0499</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04378</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.04686</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04676</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.20145</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14404</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.29174</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29648</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30633</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.30156</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29662</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.294</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.2952</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29426</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29874</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29243</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29647</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.27043</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29541</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29955</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30955</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30576</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30285</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31621</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.32022</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34939</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.35146</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.34633</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.36837</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36683</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33697</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.33203</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.32074</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31226</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.40641</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.35168</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32228</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30976</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31622</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30303</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.2827</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.2969</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29259</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28968</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28273</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27267</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27264</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.28252</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.1736</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.15985</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17242</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14891</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.16064</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15994</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23836</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.21536</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22791</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.27105</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.2875</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29229</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.32093</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.29257</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28273</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.28257</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28229</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.26935</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28233</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32436</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31209</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30681</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.31806</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.3103399999999999</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.36007</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.3143</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.27495</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.37772</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.38119</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.42063</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.43358</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33019</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.40993</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.40669</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.38987</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.39584</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.29977</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30097</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29877</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.30007</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15736</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.28388</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.309</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.3115</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.30666</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32188</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34214</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30043</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33039</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38256</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.50747</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79111</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6218899999999999</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.39985</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49775</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.78083</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.91995</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49424</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.92304</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.89209</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.31109</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.38147</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.9150499999999999</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.6361</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.2141</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.882</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.56533</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.35863</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.05194</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.55874</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.8148099999999999</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.53084</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.79692</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.7965399999999999</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8797200000000001</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.8863799999999999</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.5155299999999999</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.42051</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.42865</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.4755</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.23575</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87966</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55152</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.65035</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.54543</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.50589</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.4593</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42761</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.44217</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.45129</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.39537</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45305</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.42147</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.35553</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.40029</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.36551</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.39265</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41516</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.43421</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.3442</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.39111</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.35082</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.36325</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.35902</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.36024</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.40999</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.36185</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.45113</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.35766</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.39986</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.40057</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.58866</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.42841</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.59661</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.6015499999999999</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.65623</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.45153</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.40723</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.56028</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.44636</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.86188</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.6508200000000001</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.8289099999999999</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>0.81187</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.84902</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.32723</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.43246</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.32924</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.32465</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.30194</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.28909</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.42121</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.29348</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.2711</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.3066</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.3583</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.33244</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.31957</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.33919</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.33972</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.31775</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.30621</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31907</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.31974</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.34432</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.31475</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.31488</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.32069</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.31587</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.32646</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.31238</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.31388</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.31248</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.3152799999999999</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.30985</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.31637</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.32303</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.32629</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.3555</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.34193</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.34016</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.33892</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.33062</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.33744</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.33556</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.41033</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.41304</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.45289</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.4154</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.39184</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.37529</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.35338</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32999</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.98602</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.36084</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.48706</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.44952</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.5425800000000001</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.6104700000000001</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.40258</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.41004</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.41728</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.45744</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.41187</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.35895</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.38838</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.33085</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35951</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.34602</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32326</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.40053</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.50073</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.35746</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.38801</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.34379</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.35116</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.35554</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.37085</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.3577</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.36285</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.31626</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.31337</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33238</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.33795</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.33795</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.34949</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.31536</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.3025</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.29046</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.30332</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.28892</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.27762</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.16456</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.281</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.30788</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.32952</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.30374</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.31162</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.2968</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.26082</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.20052</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.2775</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.2554</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.33964</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.27496</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.31235</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.31757</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.33902</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.35756</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.3202</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.3121</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.31983</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.30505</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.31301</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.28978</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.30215</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.29114</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.30916</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.32047</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.31157</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.28987</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.34749</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.2554</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.35021</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.32215</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.26995</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.352</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.27547</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.34931</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.32885</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.33846</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.31006</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.34937</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.3167</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.38541</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.32303</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.43204</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.27829</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.42323</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.35062</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44778</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.31814</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.42076</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35908</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.40207</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.40081</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.5978300000000001</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.35053</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.88966</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.35035</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.14058</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.7072000000000001</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.7999299999999999</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.65234</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.58756</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.45121</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.45042</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.50054</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.43998</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.43774</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41512</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.41299</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.42378</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.5011</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.41299</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.43415</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.41329</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.43418</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.39048</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.42846</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.45091</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39639</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.42356</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.43456</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.41299</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.41296</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.40061</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.42399</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.39638</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.40283</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.54569</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.37083</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.35331</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.29674</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.36713</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.36012</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.30062</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.33031</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.29916</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.31654</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.3087</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>0.05937</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.6257</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.39464</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.32129</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.24994</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.04433</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.6535299999999999</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.21832</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.32574</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.3092</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>0.33912</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.5317200000000001</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30251</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.26526</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.26098</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.29572</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.26558</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.28869</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.37641</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.2939</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.33885</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.29432</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.30755</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.31911</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.31436</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.34011</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.33831</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.38558</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.34679</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.35924</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.3396</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.33531</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.37171</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.43618</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.35993</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.40502</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.36401</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.35235</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.58578</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.46444</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.71634</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.46579</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.43866</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.37611</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.42459</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.38738</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.37047</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.33541</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.34172</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.33034</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.32567</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.31943</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.42467</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.3405</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.34536</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.34134</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.33684</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.32742</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.33067</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.32748</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.32616</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.32549</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.31115</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.32838</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.32721</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.32082</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.31688</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.32135</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.32133</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.31093</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.32584</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.3119</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.32108</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.3216</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.39293</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.32698</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.35104</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.40143</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.3762799999999999</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.3508</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.33955</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.35594</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.33295</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.33473</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.3192</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.26577</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.33287</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.32134</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.27412</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.3055</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.29195</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.23581</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.14491</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.14721</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.29653</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.15407</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.14437</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.14075</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.14413</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.14258</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.25736</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.14467</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.26668</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.26707</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.14211</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.0338</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.11413</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.11325</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.14532</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.14146</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.14664</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.28733</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.32391</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.33094</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.32296</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.34689</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31687</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.35745</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.35007</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.38075</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.34404</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.38061</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.34673</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.39913</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.36133</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.38563</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.4508</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.40067</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.39321</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.40287</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.39874</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.4411</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.44104</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.44043</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.44537</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.44483</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.40344</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.3912</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.39838</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.39215</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.36052</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.36121</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.34888</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.35006</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.34039</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.54872</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.3897</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.46973</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.42477</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.41681</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.37047</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.38191</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.38116</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.39395</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.38065</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.37016</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.38066</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.36041</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.39154</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.37062</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.38071</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.35055</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.34756</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.35556</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.34516</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.34049</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.34049</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.34511</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.35585</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.3706</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.38043</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.36019</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.34019</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.34048</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.34048</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.33092</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.34582</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.35488</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.39373</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.27601</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.3108399999999999</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31058</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.30426</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.27222</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.27562</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.24681</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.24219</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.18448</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.28337</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.24082</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.22259</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.24801</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.29309</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.27511</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.30857</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.27011</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.2878</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.29087</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.28837</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.2849</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.27245</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.22263</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.30503</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.28312</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.29897</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.28105</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.26445</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.31442</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.33524</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.32652</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.32059</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.30673</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.33016</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.34998</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.34776</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.36409</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.36463</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.37851</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.41186</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.41887</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.24363</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.39322</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.38235</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.35456</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.35717</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.35484</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.41811</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.44365</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.34814</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.36754</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.37047</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.36042</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.38073</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.38054</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.38568</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.35038</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.36054</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.3403</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.36645</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.4201</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.37081</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.39223</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.381</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.35298</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.34979</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.36059</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.35197</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.34221</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.34797</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.34598</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.34996</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.3473</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.34998</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.34085</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.34236</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.34338</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.33875</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.33854</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.34029</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.33082</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.34138</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.33253</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.35048</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.34455</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.36184</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.31324</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.32947</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.33947</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.32588</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.31907</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.33221</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.32105</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.30924</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.3557</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.33467</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.28244</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.37388</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.41187</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.29908</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.39488</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.2773</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.26822</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.3386</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>-0.03718</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.25257</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.25007</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.20083</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.07165000000000001</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.18102</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.24485</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.28585</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.31204</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.26952</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.25127</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.28725</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.30086</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.29537</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.2705</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.29614</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.32897</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.32552</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.32418</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.41209</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.33424</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.32744</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.33538</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.34462</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.30482</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.3111</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.31561</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.32096</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.33064</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.32263</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.46885</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.40567</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.73339</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.35464</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.41005</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.34673</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.33088</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.33872</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.46588</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.35296</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.40341</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.30322</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.34224</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.3449</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.34563</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.31713</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.31105</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.31804</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.30102</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.33761</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.30496</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.34074</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.33214</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.32852</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.32537</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.3304</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.32539</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.32563</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.32473</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.32401</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.32661</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.32453</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.32745</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.32873</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.3273</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.32768</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.32423</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.33134</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.3265</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.32114</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.31982</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.32311</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.32653</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.33112</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.33549</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.34661</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.34112</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.34123</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.33576</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.3391</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.32158</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.32136</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.33449</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.34993</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.35439</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.33446</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.32439</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.31662</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.32363</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.31629</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.33839</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.28525</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.34306</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.34184</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.29671</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.32615</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.28188</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.32505</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.3187</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.32034</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.32582</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32868</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.33362</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.33127</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.31387</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.32691</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.31965</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.32016</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.31361</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.34928</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.30419</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.28595</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.31562</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.34476</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.32478</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.34096</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.33186</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.35013</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.35016</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.35018</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.36029</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.32681</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.32975</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.34796</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.37857</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.36947</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.36394</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.37037</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.36478</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.3756</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.36299</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.39677</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.38579</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.37169</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.40463</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.35506</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.38073</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.37201</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.3613</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.35066</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.35011</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.34999</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34937</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.33992</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.35196</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.35749</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.35698</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.35176</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.35091</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.35011</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.34991</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.34977</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.3466</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.36101</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.3474100000000001</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.35077</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33718</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.3399</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.3401</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.33998</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.36999</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32444</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.33868</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.3399</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.34995</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.337</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.34002</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.3451</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.33622</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.34993</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.34993</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.33662</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.34023</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.3283</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.34898</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.34006</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.3364</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.28881</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.32638</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.32776</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.32886</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.32546</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.31844</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.32763</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.31853</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.3186</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.3291</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.32517</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32914</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31909</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37094</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32474</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.32059</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.31838</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.31544</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.32406</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.32391</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.32764</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.32145</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.32304</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.32981</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.33033</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.33633</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.34571</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.35878</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.59972</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.39668</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.35476</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.3553</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.36678</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.35068</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.3603</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.34746</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.36057</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.36049</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36252</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.35046</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.37971</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.38053</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.38175</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.38372</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.4348399999999999</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.41112</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.38806</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.38672</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.6762100000000001</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.88144</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.48452</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.42109</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.46638</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.39403</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.35096</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.35082</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.35993</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.34011</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.34506</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.3174</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.41569</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.37739</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.37217</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.36328</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.35988</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.35974</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.36283</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.35956</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.36097</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.35982</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.35375</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.36078</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.36096</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.35705</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.35244</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.35992</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.36026</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.35991</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.34378</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.37106</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35883</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.35655</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.36013</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.36013</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.38134</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36599</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.38139</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35657</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35654</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.35118</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.35187</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35848</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.35001</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.33001</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.32007</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.33161</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.32194</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.2609</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.13446</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.29016</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.28405</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.28252</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.19488</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.24539</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.27838</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>-0.0225</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.27961</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.11239</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>-0.0224</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.28404</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.23078</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.28701</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.24049</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.30301</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.30272</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.14431</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.29622</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.21004</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.21726</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.2835</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.28585</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.29719</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.29681</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.30372</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.29231</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.31039</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.33562</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.33971</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.34004</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.29634</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.34187</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.41769</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.3696</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.41421</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.6820499999999999</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.64224</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.63763</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.47873</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.6637999999999999</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.48933</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.84353</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.45858</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.47206</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.4060299999999999</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.37834</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.35648</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.49087</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.43649</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.42481</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.38009</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.37579</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.36758</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.36023</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34584</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.50206</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.48412</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.47765</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.46571</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.42394</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.40202</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.40865</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.41604</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.41334</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.42248</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.40308</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.39892</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.41618</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.41349</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.39584</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.389</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.42287</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.38916</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.42086</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.39177</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.40263</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.40256</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.41646</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.40249</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.45753</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.45656</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.57796</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.5122599999999999</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.45769</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.36791</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.41423</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.3893</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.32727</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.3679</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.37811</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.42645</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.37665</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.41735</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.3456</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.28678</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.31837</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.34177</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.37361</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.36319</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.3783</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.29325</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.24629</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.26853</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.12772</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>-0.00343</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>-0.00885</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.30325</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.31173</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.65906</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.34499</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.2715</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.1239</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.08643000000000001</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>-0.03666</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.26053</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>-0.00401</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.32812</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.32526</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.31505</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.32802</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.35016</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.32994</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.34276</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.33549</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.34304</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.34254</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.32749</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.35721</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.4239</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.49638</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.43464</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.5205599999999999</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.5225599999999999</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.41348</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.60284</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.7360399999999999</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.73511</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.7121499999999999</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.80171</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.56952</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.53755</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.8699</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.7985</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.6335700000000001</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.68831</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.42646</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.45843</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.4938</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.4892</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.4826</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.42388</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.5566599999999999</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.43047</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.46669</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.44343</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.43178</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.45574</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.42243</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.40346</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.4662</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.40187</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.41043</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.40148</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.39014</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.38057</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.37523</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.36013</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35693</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.3659</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.37744</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.37141</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.36033</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.35999</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.3659</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.38789</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.39158</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.38011</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.36674</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.36154</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35525</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.37989</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.39978</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.36831</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.38808</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.39692</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.42838</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.38795</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.3517</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.36884</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.34337</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.32627</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.27537</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.29441</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.15618</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.34817</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.27721</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.33902</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>-0.04986</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.31781</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.34556</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.40724</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.36596</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.45373</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.40193</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.4644</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.31513</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.30987</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>-0.04375</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.18351</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.3034</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.29291</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.31792</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.35289</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.3504</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.34838</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.34869</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.36644</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.36737</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.36049</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.39792</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.40851</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.36267</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.4104100000000001</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.40177</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.3934</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.37269</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.35858</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.3779</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.3851</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.40793</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.40167</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.34389</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.36459</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.37832</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.40005</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.36013</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.37984</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35513</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.3999</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.38087</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.37515</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.36071</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.3939</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.37906</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.36407</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.3316</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.44393</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.35699</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.37977</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.38016</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.35593</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.37769</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.35097</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.37786</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.36324</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.35713</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.35468</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.35149</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.35829</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.34756</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.35067</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.34898</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.3401</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.33176</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.34007</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.34063</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.33577</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.34078</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.34579</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.33146</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.3308</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.33927</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.33938</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.34557</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.32676</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.31778</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.31204</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.32591</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.2496</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.32781</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.32233</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.31674</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.23269</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.29434</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.23418</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.23435</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.24768</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.00319</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.13311</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.23337</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.2878500000000001</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.01101</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.16003</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.04343</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.25613</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>-0.00397</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.14524</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.15361</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.03045</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.30332</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>-0.03963000000000001</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.21778</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.23022</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.15399</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.21654</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.26784</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.28367</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.2648</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.30314</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.3267</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.29134</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.35046</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.34698</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.35054</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.35199</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.34965</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.33469</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.33103</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.36249</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.35186</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.34358</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.30933</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.35216</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.35542</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.36994</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.35418</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.36248</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.36526</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.36122</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.34489</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.36049</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.37412</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.34331</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.36614</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.37091</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.36081</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.35045</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.35082</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.35032</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.35081</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.35228</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.32339</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.32464</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.33912</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.34293</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.34056</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.34015</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.33231</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.32575</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.32064</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.32027</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.31138</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.3107799999999999</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.31559</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.31085</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.3118</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.31165</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.31148</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.31821</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.30747</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.30747</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.30997</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.31093</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.30683</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.30747</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.30809</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.31085</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.31208</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.29165</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.22728</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.21733</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.15131</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.18034</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.08563999999999999</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.0162</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>-0.00148</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>-0.04252</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.06579</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>-0.03308</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.04146</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>-0.03215999999999999</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.04375</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.04822</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.04579</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.16998</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.21507</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.27723</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.24502</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.24612</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.24665</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.25089</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.26374</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.28698</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.27232</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.26888</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.25728</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.30353</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.27714</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.28068</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.26571</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.28021</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.26799</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.28402</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.27389</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.29365</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.36173</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.30053</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.30512</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.2852</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.25547</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.26697</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.25146</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.23509</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.17944</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.057</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29795</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.41025</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.01831</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.06619</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.25013</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.22587</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.22589</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.14583</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.27012</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.26172</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.2439</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.22256</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.2067</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.19004</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.21398</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.22642</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.17035</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.19053</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.22344</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.22032</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.24465</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.23271</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.21546</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.26166</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.22616</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.26943</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.32792</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.27139</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.24695</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.24996</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.18459</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.06587999999999999</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.49289</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.50134</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.5510900000000001</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.38165</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.07895000000000001</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.2309</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>-0.01786</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.203</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.09451999999999999</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.04396</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.05724</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>-0.00552</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.20847</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.03348</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.29087</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.004690000000000001</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>-0.04665999999999999</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.02794</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.13141</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>-0.03839</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.04187</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.0366</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.08343</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.02742</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.02011</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.03026</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.04914</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.23857</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.2829100000000001</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.25637</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.2847</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.31007</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.3115</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.30773</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.32224</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.32438</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.31657</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.31887</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.33514</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.33112</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.34947</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.32779</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.34825</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.35521</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.23631</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.35023</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.34949</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.34164</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>0.35118</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.34423</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.36763</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.33727</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.34813</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.35743</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.32361</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.32964</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.3298</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.33095</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.32839</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.34001</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.32531</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33022</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.3554</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.36747</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.33274</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.33666</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.33587</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.33121</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.33114</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.33138</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.33396</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.32938</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.34206</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.33543</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.33459</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.32777</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.34464</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.11371</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.32701</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.32728</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.32149</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.33154</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.32901</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.33025</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.33239</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.3361</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.34369</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.29916</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.42241</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.27424</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.32643</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.26248</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.15649</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.25286</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.35734</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.31623</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.3193</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.39535</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.31376</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.40191</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.33776</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.33178</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.32172</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.34743</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.30352</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.30923</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.30717</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.3132</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.29007</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.11495</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.25989</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.26976</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30409</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.31124</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.16742</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.31898</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.31758</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.15075</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.07395</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.30906</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.29022</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.31041</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.31656</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.32116</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.32657</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.33682</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32401</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.3472</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.34132</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.33977</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.34099</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.34214</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.34722</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.33243</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.35031</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.34922</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.33532</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.34586</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.34389</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.34891</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.37186</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.3165</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.33734</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.36148</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.38571</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.34586</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.35897</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.3505</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.35523</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.3486</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.36806</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.3526</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.31472</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.33218</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.32602</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.33094</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.33119</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.37099</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.33118</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.33117</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.26347</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.31655</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.3203</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.3287</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.32939</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.33084</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.33198</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.33597</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.34521</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.28828</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.34941</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.34084</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.33634</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.32114</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.32085</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.33139</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.34662</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.33126</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.34036</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.35426</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.32338</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.36945</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.35544</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.36972</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.3595</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.34979</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.28473</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.33017</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.34392</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.3435299999999999</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.51339</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.28675</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.50744</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.27158</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.28619</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.31403</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.34864</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.29246</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.26652</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.28718</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.27752</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.26221</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.18016</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.26298</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.36796</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.27992</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.2606</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.2597</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.2927</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.34519</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.34637</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32724</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.23999</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.27787</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.32327</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.3058999999999999</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.26676</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.28062</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.30272</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.35438</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.42428</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.40765</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.47561</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.48906</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.46882</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.47962</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.38548</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.08733</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.38019</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.40889</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.44171</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.32278</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.40537</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.35008</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.47538</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.43647</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.37762</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.42261</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.42576</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.73997</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.45358</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.40679</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.45948</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.40201</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.37977</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.39215</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.37147</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.37067</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.37277</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.36891</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.369</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.34706</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.46946</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.40031</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.40038</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.39069</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.38084</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.36023</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.37564</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.37445</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.37875</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.37738</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.36926</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.36695</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.36157</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.36005</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.35991</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.36045</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.356</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.32912</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.35625</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.35128</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.34986</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.3473</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.35014</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.3604</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.37126</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.40012</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.37603</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.36936</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.35167</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.34136</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.30483</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.34198</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.32183</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.32863</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.30202</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.40266</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.35255</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.31442</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.35076</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.21558</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.33838</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.1615</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.34952</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.24139</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.35797</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.34021</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.34044</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29254</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.29445</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.31254</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.31807</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.27237</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.31952</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.3381</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.33724</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.17591</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.30307</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.27837</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.28377</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.30268</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.31432</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.31798</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.34748</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.33848</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.35047</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.33307</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.36565</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.43954</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.36705</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.41307</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.39746</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.39292</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.4669700000000001</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.56249</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.55875</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.38545</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.4595</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.5481200000000001</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.46622</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.35382</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.49887</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.4024</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.5377000000000001</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.52971</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.7312799999999999</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.77408</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.55064</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.55279</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.39869</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.44376</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.39187</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.37471</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.37936</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.36999</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.37565</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.27353</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.36988</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.31965</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.37122</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.3356</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.3383</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.35072</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.32177</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.33538</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.34427</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.33913</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.33976</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.34621</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.33617</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.33782</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.33676</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.3146</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.32819</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.32014</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.30998</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.30527</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.3093</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.30969</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.2929</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.29254</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.34554</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.3638</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.30496</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.29106</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.28643</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.28078</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.27434</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.3148</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.26052</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.26146</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.27675</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.21083</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.23522</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.16915</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.01519</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.0054</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.14296</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.01835</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>-0.02278</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.15567</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>-0.0421</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>-0.04943</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>-0.04033</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>-0.02322</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.23443</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>-0.04017</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.02281</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.0338</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.02673</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.02911</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.01485</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.0319</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.12309</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.08123000000000001</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.1341</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.16762</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.20279</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.25157</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.19187</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.16472</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.32846</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.30668</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.32445</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.31399</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.34383</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.22572</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.32545</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.3354</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.3282</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.27012</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.36372</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.38517</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.37107</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.36683</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.34902</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.39576</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.37734</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.37668</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.40219</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.38322</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.36289</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.36904</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.36724</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.41986</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.38388</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.37952</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.37584</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.38817</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.3785</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.35284</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.8149</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.3435299999999999</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.40405</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.38202</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.33842</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.33939</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.35578</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.35306</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.38382</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.34657</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.34785</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.34307</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.38153</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.35583</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.36248</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.38057</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.37948</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.34861</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.36129</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.36403</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.36213</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.36548</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.35642</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.36712</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.35246</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.36809</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.34111</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.32252</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.32412</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.3039</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.30411</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.297</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.29606</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.28536</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.26299</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.25308</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.22483</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.22384</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.22836</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.24503</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.09059</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.0141</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.01351</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.01239</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.03345</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.12277</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.03177</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>-0.006849999999999999</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.01668</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.04374</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.01132</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.00784</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.01247</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.1546</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.18391</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.03645</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.17984</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.13705</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.16084</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.18866</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.20766</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.27043</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.20344</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.2773</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.22957</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.25533</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.33573</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.31248</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.46218</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.40933</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.40043</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.36288</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.3716</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.38952</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.36254</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.34196</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.38898</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.5170800000000001</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.41668</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.39106</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.37782</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.39253</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.38722</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.37979</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.40164</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.36148</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.39321</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.4234</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.3931</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.38709</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.37702</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.38421</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.37365</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.36085</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.38587</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.32916</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.52367</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.39057</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.39375</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.31501</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.36942</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.35963</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.36592</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.34612</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.41977</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.34491</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.37638</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.37349</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.34258</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.34121</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.35055</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.33382</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.31781</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.35068</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.3242</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.32147</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.33343</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.3645</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.3405899999999999</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.35392</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.34095</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.34968</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.3420899999999999</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.32377</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.29232</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.25449</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.21853</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.1993</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.12694</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.17637</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.20052</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.19537</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.09789</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.12535</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.06056</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.07922</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.04324</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.04415</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.04417</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.04383</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.04348</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.04405</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.06919</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.02967</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.05926</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.08295999999999999</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.14081</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.15927</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.10206</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.20948</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.1828</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.10416</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.04724</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.23755</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.11839</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.10154</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.20896</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.15629</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.19341</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.20211</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.17337</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.21187</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.23671</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.23805</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.2554</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.28174</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.28536</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.28769</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.30878</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.36016</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.39248</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.34312</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.33006</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.29919</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.34693</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.39111</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.37258</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.38094</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.3686</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.38622</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.40737</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.42069</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.49595</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.40863</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.41168</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.42923</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.41029</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.39163</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.4081</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.40939</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.38418</v>
       </c>
     </row>
   </sheetData>
